--- a/vendor/ironcalc/xlsx/tests/docs/DATE.xlsx
+++ b/vendor/ironcalc/xlsx/tests/docs/DATE.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Documents\IronCalc work\Function descriptions\Date and Time\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc/xlsx/tests/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443ECD5D-BBC2-4C12-B0BD-C579F6B3F12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6FD8C1-913C-D549-917A-0701025B0365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DATE" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -66,18 +66,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -97,15 +108,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,14 +455,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" style="1" customWidth="1"/>
+    <col min="1" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -462,21 +474,21 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
         <v>1905</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="5">
         <f>DATE(A2,B2,C2)</f>
         <v>1828</v>
       </c>
@@ -485,18 +497,18 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
         <v>2000</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>15</v>
       </c>
-      <c r="D3" s="3">
-        <f t="shared" ref="D2:D8" si="1">DATE(A3,B3,C3)</f>
+      <c r="D3" s="5">
+        <f t="shared" ref="D3:D8" si="1">DATE(A3,B3,C3)</f>
         <v>36692</v>
       </c>
       <c r="E3" s="4">
@@ -504,17 +516,17 @@
         <v>36692</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
         <v>2024</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <v>12</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>25</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <f t="shared" si="1"/>
         <v>45651</v>
       </c>
@@ -523,17 +535,17 @@
         <v>45651</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
         <v>2025</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>12</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>25</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <f t="shared" si="1"/>
         <v>46016</v>
       </c>
@@ -542,17 +554,17 @@
         <v>46016</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
         <v>2025.9</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>12.9</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>25.9</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="5">
         <f t="shared" si="1"/>
         <v>46016</v>
       </c>
@@ -561,17 +573,17 @@
         <v>46016</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
         <v>2030</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="5">
         <f t="shared" si="1"/>
         <v>47484</v>
       </c>
@@ -580,17 +592,17 @@
         <v>47484</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
         <v>9999</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>12</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>31</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="5">
         <f t="shared" si="1"/>
         <v>2958465</v>
       </c>
@@ -599,8 +611,11 @@
         <v>2958465</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D9" s="3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5">
         <f>DATE(2024, 11, 22)</f>
         <v>45618</v>
       </c>
